--- a/examples/sixdrive12resp/results/case/sdynpy_frame6x12_profile_backup_before_octave.xlsx
+++ b/examples/sixdrive12resp/results/case/sdynpy_frame6x12_profile_backup_before_octave.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/case/sdynpy_frame6x12_system_nonlinear_allmodes.npz</t>
+          <t>/Users/nhunterjr/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/case/sdynpy_frame6x12_system_nonlinear_allmodes.npz</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/control_laws/optimal_diagonal_control.py</t>
+          <t>/Users/nhunterjr/Code/python/rattlesnake-vibration-controller/control_laws/optimal_diagonal_control.py</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/case/flat_spec_frame6x12.mat</t>
+          <t>/Users/nhunterjr/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/case/flat_spec_frame6x12.mat</t>
         </is>
       </c>
     </row>
